--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>443.44</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>0 de 20</t>
+          <t>1 de 20</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2291,7 +2291,7 @@
         <v>96.37</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>172.99</v>
+        <v>616.4299999999999</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>96.37</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>206.52</v>
+        <v>649.9599999999999</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0</v>
+        <v>1496.72</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>33.53</v>
+        <v>3090.85</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>1166.4</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>867.5599999999999</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -1309,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2345.61</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>1496.14</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1698,137 +1698,197 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>1 de 20</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>1 de 20</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1 de 20</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>0 de 20</t>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>1 de 21</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1 de 21</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>1 de 21</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>2 de 21</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>3 de 21</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1851,7 +1911,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2156,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>1496.72</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2210,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>33.53</v>
+        <v>3090.85</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2237,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
+        <v>5875.71</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -2305,14 +2365,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4780.84</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -2332,14 +2392,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>1391.04</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>4780.84</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -2359,7 +2419,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2386,7 +2446,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2413,39 +2473,66 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="4" t="n">
         <v>3203.07</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D23" s="4" t="n">
         <v>14896.46</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E23" s="4" t="n">
         <v>96.37</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>649.9599999999999</v>
-      </c>
-      <c r="G22" s="4" t="n">
+      <c r="F23" s="4" t="n">
+        <v>11079.71</v>
+      </c>
+      <c r="G23" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>172.99</v>
+        <v>630.91</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>443.44</v>
+        <v>591.25</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
@@ -2351,7 +2351,7 @@
         <v>96.37</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>616.4299999999999</v>
+        <v>1222.16</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>96.37</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11079.71</v>
+        <v>11685.44</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -637,10 +637,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>284.4</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>104.4</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>110.05</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1496.72</v>
+        <v>1520.11</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1345,7 +1345,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1818,44 +1818,44 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t>2 de 21</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
           <t>1 de 21</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>0 de 21</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>1 de 21</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>1 de 21</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>0 de 21</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>0 de 21</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
           <t>2 de 21</t>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>3 de 21</t>
+          <t>4 de 21</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>498.85</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -2216,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1496.72</v>
+        <v>1520.11</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2324,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -2530,7 +2530,7 @@
         <v>96.37</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>11685.44</v>
+        <v>14927.52</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARBOLEDA ZAMBRANO ROBERTO ANTONIO</t>
+          <t>ARBIZACONSTRUC S.A.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARELLANO CEDEÑO DANNY MARCELO</t>
+          <t>ARBOLEDA ZAMBRANO ROBERTO ANTONIO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
+          <t>ARELLANO CEDEÑO DANNY MARCELO</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BAESCORP S.A.S.</t>
+          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
+          <t>BAESCORP S.A.S.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1520.11</v>
+        <v>0</v>
       </c>
       <c r="N11" s="2" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3090.85</v>
+        <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
         <v>0</v>
@@ -1278,17 +1278,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1166.4</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>867.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -1309,10 +1309,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>2345.61</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1496.14</v>
+        <v>1520.11</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1338,14 +1338,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -1398,14 +1398,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>630.91</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1429,10 +1429,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>591.25</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>3090.85</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>1166.4</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>867.5599999999999</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>2345.61</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>1496.14</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1518,14 +1518,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>630.91</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1609,7 +1609,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>591.25</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1758,137 +1758,377 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>1 de 21</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>2 de 21</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>1 de 21</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>1 de 21</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>1 de 21</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>2 de 21</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>4 de 21</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>0 de 21</t>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>2 de 25</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>1 de 25</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>2 de 25</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>4 de 25</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>0 de 25</t>
         </is>
       </c>
     </row>
@@ -1903,7 +2143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2014,11 +2254,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARBOLEDA ZAMBRANO ROBERTO ANTONIO</t>
+          <t>ARBIZACONSTRUC S.A.</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0</v>
+        <v>633.6</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -2041,11 +2281,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARELLANO CEDEÑO DANNY MARCELO</t>
+          <t>ARBOLEDA ZAMBRANO ROBERTO ANTONIO</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -2068,11 +2308,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
+          <t>ARELLANO CEDEÑO DANNY MARCELO</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -2095,7 +2335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BAESCORP S.A.S.</t>
+          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2122,7 +2362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
+          <t>BAESCORP S.A.S.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2149,7 +2389,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2176,11 +2416,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1382.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0</v>
@@ -2203,7 +2443,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2216,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1520.11</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -2230,7 +2470,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2257,20 +2497,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0</v>
+        <v>1382.33</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>835.22</v>
+        <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>3090.85</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2284,11 +2524,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>89.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -2297,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>5875.71</v>
+        <v>1520.11</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -2311,20 +2551,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8791.290000000001</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -2338,20 +2578,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>253.44</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>835.22</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>96.37</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1222.16</v>
+        <v>3090.85</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2365,11 +2605,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2378,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>5875.71</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2392,20 +2632,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>4780.84</v>
+        <v>8791.290000000001</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2419,20 +2659,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>253.44</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>96.37</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>1222.16</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2446,7 +2686,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2473,14 +2713,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>1391.04</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>4780.84</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -2500,39 +2740,147 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="4" t="n">
-        <v>3203.07</v>
-      </c>
-      <c r="D23" s="4" t="n">
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="4" t="n">
+        <v>3836.67</v>
+      </c>
+      <c r="D27" s="4" t="n">
         <v>14896.46</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E27" s="4" t="n">
         <v>96.37</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F27" s="4" t="n">
         <v>14927.52</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>166.61</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3090.85</v>
+        <v>3124.48</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>1 de 25</t>
+          <t>2 de 25</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -2510,7 +2510,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
+        <v>166.61</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3090.85</v>
+        <v>3124.48</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>96.37</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>14927.52</v>
+        <v>15127.76</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>110.05</v>
+        <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1520.11</v>
+        <v>1496.72</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>4 de 25</t>
+          <t>3 de 25</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>498.85</v>
+        <v>388.8</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1520.11</v>
+        <v>1496.72</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>96.37</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>15127.76</v>
+        <v>14994.32</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>DELGADO LOOR JORGE ARTURO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>DISALME CIA. LTDA.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>166.61</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1496.72</v>
+        <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>166.61</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3124.48</v>
+        <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
         <v>0</v>
@@ -1458,17 +1458,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1166.4</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>867.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2345.61</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1496.14</v>
+        <v>1496.72</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1518,14 +1518,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>630.91</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>591.25</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>3124.48</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>1166.4</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>867.5599999999999</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1669,10 +1669,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>2345.61</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>1496.14</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1698,14 +1698,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1758,14 +1758,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>630.91</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>591.25</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -1998,137 +1998,437 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VERA ARCE MARIA ISABEL</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>1 de 25</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>2 de 25</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>2 de 25</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>1 de 25</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>1 de 25</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>2 de 25</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t>3 de 25</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>0 de 25</t>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>2 de 30</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2 de 30</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>1 de 30</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2 de 30</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>3 de 30</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>0 de 30</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2416,7 +2716,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -2443,7 +2743,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>DELGADO LOOR JORGE ARTURO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2470,7 +2770,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>DISALME CIA. LTDA.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2497,11 +2797,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1382.33</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0</v>
@@ -2510,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>166.61</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
@@ -2524,7 +2824,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2537,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1496.72</v>
+        <v>0</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>0</v>
@@ -2551,7 +2851,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2578,20 +2878,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>1382.33</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>835.22</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>3124.48</v>
+        <v>166.61</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2605,11 +2905,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>89.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2618,7 +2918,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5875.71</v>
+        <v>1496.72</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2632,20 +2932,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8791.290000000001</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2659,20 +2959,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>253.44</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>835.22</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>96.37</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1222.16</v>
+        <v>3124.48</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2686,11 +2986,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -2699,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>5875.71</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2713,20 +3013,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4780.84</v>
+        <v>8791.290000000001</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -2740,20 +3040,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>253.44</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>96.37</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>1222.16</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -2767,7 +3067,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -2794,14 +3094,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>1391.04</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>4780.84</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -2821,7 +3121,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2848,39 +3148,174 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>VERA ARCE MARIA ISABEL</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" s="4" t="n">
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="4" t="n">
         <v>3836.67</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D32" s="4" t="n">
         <v>14896.46</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E32" s="4" t="n">
         <v>96.37</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <v>14994.32</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="VENTAS POR GRUPO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="VENTA MENSUAL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CUMPLIMIENTO MENSUAL" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -68,6 +69,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -3322,4 +3327,149 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ASESOR</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GRUPO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VENTA</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>POR CUMPLIR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CUMPLIMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8260.549999999999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>-8260.549999999999</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PANELES PVC Y PU</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>8806</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5973.76</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2832.24</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.6783738360208948</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>8921</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>14234.31</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>-5313.309999999999</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.595595785225872</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -440,11 +440,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>FRANQUICIA DISTRIBUIDORA SANTA MARIA FRADISAMA S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>166.61</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>166.61</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1496.72</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>1496.72</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3124.48</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1166.4</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>867.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -1674,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>2345.61</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1496.14</v>
+        <v>3124.48</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1703,17 +1703,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>1166.4</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>867.5599999999999</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>2345.61</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>1496.14</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1763,14 +1763,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>630.91</v>
+        <v>2719.84</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>591.25</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
@@ -1823,14 +1823,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>630.91</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>591.25</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2303,137 +2303,197 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>1 de 30</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>2 de 30</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>2 de 30</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>1 de 30</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>1 de 30</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>2 de 30</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>3 de 30</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>0 de 30</t>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>2 de 31</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2 de 31</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>2 de 31</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>3 de 31</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
         </is>
       </c>
     </row>
@@ -2448,11 +2508,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2829,7 +2889,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>FRANQUICIA DISTRIBUIDORA SANTA MARIA FRADISAMA S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2856,7 +2916,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2883,11 +2943,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1382.33</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0</v>
@@ -2896,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>166.61</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2910,11 +2970,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>1382.33</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2923,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1496.72</v>
+        <v>166.61</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2937,7 +2997,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2950,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>1496.72</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2964,20 +3024,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>835.22</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>3124.48</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2991,20 +3051,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>89.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>835.22</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5875.71</v>
+        <v>3124.48</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3018,20 +3078,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8791.290000000001</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2719.84</v>
+        <v>5875.71</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -3045,20 +3105,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>253.44</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>8791.290000000001</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>96.37</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1222.16</v>
+        <v>2719.84</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3072,20 +3132,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>253.44</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>96.37</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>1222.16</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3099,14 +3159,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1391.04</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4780.84</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
@@ -3126,14 +3186,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>1391.04</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>4780.84</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -3153,7 +3213,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3180,7 +3240,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3207,7 +3267,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3234,7 +3294,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3261,7 +3321,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3288,39 +3348,66 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="4" t="n">
         <v>3836.67</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D33" s="4" t="n">
         <v>14896.46</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E33" s="4" t="n">
         <v>96.37</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F33" s="4" t="n">
         <v>14994.32</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>591.25</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>220.32</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>3 de 31</t>
+          <t>4 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>96.37</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1222.16</v>
+        <v>1442.48</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>96.37</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>14994.32</v>
+        <v>15214.64</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>8806</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5973.76</v>
+        <v>6194.08</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2832.24</v>
+        <v>2611.92</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.6783738360208948</v>
+        <v>0.7033931410401999</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>8921</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14234.31</v>
+        <v>14454.63</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-5313.309999999999</v>
+        <v>-5533.629999999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.595595785225872</v>
+        <v>1.620292568097747</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0</v>
+        <v>426.6</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>156.6</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>0</v>
+        <v>1448.77</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>475.2</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -2423,44 +2423,44 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
+          <t>3 de 31</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
           <t>2 de 31</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>2 de 31</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2 de 31</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>1 de 31</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>1 de 31</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
           <t>2 de 31</t>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>4 de 31</t>
+          <t>5 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>166.61</v>
+        <v>2198.58</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1496.72</v>
+        <v>1971.92</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>96.37</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>15214.64</v>
+        <v>17721.81</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8260.549999999999</v>
+        <v>9318.950000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-8260.549999999999</v>
+        <v>-9318.950000000001</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>8806</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6194.08</v>
+        <v>7642.85</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2611.92</v>
+        <v>1163.15</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.7033931410401999</v>
+        <v>0.8679139223256871</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>8921</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>14454.63</v>
+        <v>16961.8</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-5533.629999999999</v>
+        <v>-8040.800000000001</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.620292568097747</v>
+        <v>1.901333931173635</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>284.4</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>104.4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -1473,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>166.61</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>426.6</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>156.6</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1448.77</v>
+        <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>475.2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1496.72</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3124.48</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1707,13 +1707,13 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1166.4</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>867.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2345.61</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1496.14</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>630.91</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>591.25</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>220.32</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2418,17 +2418,17 @@
     <row r="33">
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>5 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2513,9 +2513,9 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>octubre</t>
+          <t>noviembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2596,16 +2596,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>489.11</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>489.11</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>388.8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>388.8</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>633.6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0</v>
@@ -2974,16 +2974,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1382.33</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>2198.58</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2198.58</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3007,10 +3007,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1971.92</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1971.92</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>835.22</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>835.22</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>3124.48</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>3124.48</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3082,16 +3082,16 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>89.76000000000001</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>5875.71</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>5875.71</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>8791.290000000001</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8791.290000000001</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>253.44</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>96.37</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>96.37</v>
+        <v>1442.48</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1442.48</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3190,10 +3190,10 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1391.04</v>
+        <v>4780.84</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4780.84</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -3396,16 +3396,16 @@
     </row>
     <row r="33">
       <c r="C33" s="4" t="n">
-        <v>3836.67</v>
+        <v>14896.46</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>14896.46</v>
+        <v>96.37</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>96.37</v>
+        <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>17721.81</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -3428,9 +3428,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9318.950000000001</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-9318.950000000001</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3525,16 +3525,16 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8806</v>
+        <v>10350</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7642.85</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1163.15</v>
+        <v>10350</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.8679139223256871</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3544,16 +3544,16 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>8921</v>
+        <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>16961.8</v>
+        <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-8040.800000000001</v>
+        <v>10465</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.901333931173635</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>1388.02</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>1442.48</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>1388.02</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>1388.02</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3428,9 +3428,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3528,13 +3528,13 @@
         <v>10350</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>1388.02</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>10350</v>
+        <v>8961.98</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>0.1341082125603865</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>1388.02</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>10465</v>
+        <v>9076.98</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0</v>
+        <v>0.1326344959388438</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>457.92</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>457.92</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1388.02</v>
+        <v>1845.94</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0</v>
+        <v>457.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0</v>
+        <v>-457.92</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1388.02</v>
+        <v>1845.94</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>9076.98</v>
+        <v>8619.059999999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1326344959388438</v>
+        <v>0.1763917821309126</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>2 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
         <v>3124.48</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>6.38</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1845.94</v>
+        <v>1852.32</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3528,13 +3528,13 @@
         <v>10350</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1388.02</v>
+        <v>1394.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8961.98</v>
+        <v>8955.6</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.1341082125603865</v>
+        <v>0.1347246376811594</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1845.94</v>
+        <v>1852.32</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8619.059999999999</v>
+        <v>8612.68</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1763917821309126</v>
+        <v>0.1770014333492594</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>0</v>
+        <v>1137.44</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>457.92</v>
+        <v>3240</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0</v>
+        <v>307.8</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1074.68</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>808.03</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2443,47 +2443,47 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>3 de 31</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>2 de 31</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3010,7 +3010,7 @@
         <v>1971.92</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>1137.44</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>457.92</v>
+        <v>5430.51</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1852.32</v>
+        <v>7962.35</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>457.92</v>
+        <v>5759.92</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-457.92</v>
+        <v>-5759.92</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>10350</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1394.4</v>
+        <v>2202.43</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8955.6</v>
+        <v>8147.57</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.1347246376811594</v>
+        <v>0.2127951690821256</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1852.32</v>
+        <v>7962.35</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8612.68</v>
+        <v>2502.65</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1770014333492594</v>
+        <v>0.760855231724797</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
+        <v>782.1</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1388.02</v>
+        <v>5378.75</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>2 de 31</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>1442.48</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1388.02</v>
+        <v>6160.85</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7962.35</v>
+        <v>12735.18</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5759.92</v>
+        <v>6542.02</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-5759.92</v>
+        <v>-6542.02</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>10350</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2202.43</v>
+        <v>6193.16</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8147.57</v>
+        <v>4156.84</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2127951690821256</v>
+        <v>0.5983729468599034</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7962.35</v>
+        <v>12735.18</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2502.65</v>
+        <v>-2270.18</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.760855231724797</v>
+        <v>1.216930721452461</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>1137.44</v>
+        <v>1118.05</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>1971.92</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1137.44</v>
+        <v>1118.05</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12735.18</v>
+        <v>12715.79</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6542.02</v>
+        <v>6522.63</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-6542.02</v>
+        <v>-6522.63</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12735.18</v>
+        <v>12715.79</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-2270.18</v>
+        <v>-2250.79</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.216930721452461</v>
+        <v>1.215077878643096</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5378.75</v>
+        <v>5397.84</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>2 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2983,7 +2983,7 @@
         <v>2198.58</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>1442.48</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6160.85</v>
+        <v>6179.94</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>12715.79</v>
+        <v>13345.44</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6522.63</v>
+        <v>7133.19</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-6522.63</v>
+        <v>-7133.19</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3528,13 +3528,13 @@
         <v>10350</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6193.16</v>
+        <v>6217.65</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4156.84</v>
+        <v>4132.35</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.5983729468599034</v>
+        <v>0.6007391304347826</v>
       </c>
     </row>
     <row r="5">
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>12715.79</v>
+        <v>13350.84</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-2250.79</v>
+        <v>-2885.839999999999</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.215077878643096</v>
+        <v>1.275761108456761</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>259.2</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
     <row r="33">
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
         <v>3124.48</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6.38</v>
+        <v>265.58</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>17721.81</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13345.44</v>
+        <v>13604.64</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7133.19</v>
+        <v>7392.39</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-7133.19</v>
+        <v>-7392.39</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3547,13 +3547,13 @@
         <v>10465</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>13350.84</v>
+        <v>13610.04</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-2885.839999999999</v>
+        <v>-3145.04</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1.275761108456761</v>
+        <v>1.300529383659819</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>610.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>1118.05</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>259.2</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>6.38</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>782.1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5397.84</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3240</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>307.8</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1074.68</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>808.03</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
     <row r="33">
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>3 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -2514,9 +2514,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>noviembre</t>
+          <t>diciembre</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>489.11</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>388.8</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>388.8</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -2977,13 +2977,13 @@
         <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>2198.58</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2198.58</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>610.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3004,13 +3004,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>1971.92</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1971.92</v>
+        <v>1118.05</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1118.05</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>835.22</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>3124.48</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>3124.48</v>
+        <v>265.58</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>265.58</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3085,10 +3085,10 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>5875.71</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>5875.71</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>8791.290000000001</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>96.37</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>96.37</v>
+        <v>1442.48</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1442.48</v>
+        <v>6179.94</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6179.94</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4780.84</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0</v>
+        <v>5430.51</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>5430.51</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3396,16 +3396,16 @@
     </row>
     <row r="33">
       <c r="C33" s="4" t="n">
-        <v>14896.46</v>
+        <v>96.37</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>96.37</v>
+        <v>17721.81</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>17721.81</v>
+        <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13604.64</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2508,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2517,7 +2517,6 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2551,11 +2550,6 @@
           <t>marzo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2580,9 +2574,6 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2607,9 +2598,6 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2634,9 +2622,6 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2661,9 +2646,6 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2688,9 +2670,6 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2715,9 +2694,6 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2742,9 +2718,6 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2769,9 +2742,6 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2796,9 +2766,6 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2823,9 +2790,6 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2850,9 +2814,6 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2877,9 +2838,6 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2904,9 +2862,6 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2931,9 +2886,6 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2958,9 +2910,6 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2985,9 +2934,6 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3012,9 +2958,6 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3039,9 +2982,6 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3066,9 +3006,6 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3093,9 +3030,6 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3120,9 +3054,6 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3147,9 +3078,6 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3174,9 +3102,6 @@
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3201,9 +3126,6 @@
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3228,9 +3150,6 @@
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3255,9 +3174,6 @@
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3282,9 +3198,6 @@
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3309,9 +3222,6 @@
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3336,9 +3246,6 @@
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3363,9 +3270,6 @@
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3388,9 +3292,6 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3405,9 +3306,6 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2508,7 +2508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2517,6 +2517,7 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2550,6 +2551,11 @@
           <t>marzo</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2574,6 +2580,9 @@
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2598,6 +2607,9 @@
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2622,6 +2634,9 @@
       <c r="F4" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2646,6 +2661,9 @@
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2670,6 +2688,9 @@
       <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2694,6 +2715,9 @@
       <c r="F7" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2718,6 +2742,9 @@
       <c r="F8" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2742,6 +2769,9 @@
       <c r="F9" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2766,6 +2796,9 @@
       <c r="F10" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2790,6 +2823,9 @@
       <c r="F11" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2814,6 +2850,9 @@
       <c r="F12" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2838,6 +2877,9 @@
       <c r="F13" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2862,6 +2904,9 @@
       <c r="F14" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G14" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2886,6 +2931,9 @@
       <c r="F15" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2910,6 +2958,9 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G16" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2934,6 +2985,9 @@
       <c r="F17" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2958,6 +3012,9 @@
       <c r="F18" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G18" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2982,6 +3039,9 @@
       <c r="F19" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G19" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3006,6 +3066,9 @@
       <c r="F20" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G20" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3030,6 +3093,9 @@
       <c r="F21" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G21" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3054,6 +3120,9 @@
       <c r="F22" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G22" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3078,6 +3147,9 @@
       <c r="F23" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G23" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3102,6 +3174,9 @@
       <c r="F24" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G24" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3126,6 +3201,9 @@
       <c r="F25" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G25" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3150,6 +3228,9 @@
       <c r="F26" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G26" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3174,6 +3255,9 @@
       <c r="F27" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3198,6 +3282,9 @@
       <c r="F28" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3222,6 +3309,9 @@
       <c r="F29" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3246,6 +3336,9 @@
       <c r="F30" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G30" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3270,6 +3363,9 @@
       <c r="F31" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="G31" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3292,6 +3388,9 @@
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3306,6 +3405,9 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -3422,15 +3422,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3473,17 +3473,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>240X80 PORCELANATO</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>2380</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7392.39</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-7392.39</v>
+        <v>2380</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0</v>
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PANELES PVC Y PU</t>
+          <t>FREGADEROS DE COCINA</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>115</v>
+        <v>199.5</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>115</v>
+        <v>199.5</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0</v>
@@ -3521,39 +3521,111 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>INODOROS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PANELES PVC Y PU</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>PORCELANATO</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>10350</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>6217.65</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>4132.35</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.6007391304347826</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>12350</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>12350</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>10465</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>13610.04</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-3145.04</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1.300529383659819</v>
+      <c r="C8" s="2" t="n">
+        <v>15284.5</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>15284.5</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>280.8</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>6179.94</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>280.8</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>280.8</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0</v>
+        <v>280.8</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>-280.8</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>15284.5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0</v>
+        <v>280.8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15284.5</v>
+        <v>15003.7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0</v>
+        <v>0.018371552880369</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -3430,7 +3430,7 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3600,13 +3600,13 @@
         <v>12350</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0</v>
+        <v>-5.4</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12350</v>
+        <v>12355.4</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0</v>
+        <v>-0.000437246963562753</v>
       </c>
     </row>
     <row r="8">
@@ -3619,13 +3619,13 @@
         <v>15284.5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>280.8</v>
+        <v>275.4</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15003.7</v>
+        <v>15009.1</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.018371552880369</v>
+        <v>0.01801825378651575</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>144.56</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3145,7 +3145,7 @@
         <v>6179.94</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>280.8</v>
+        <v>425.36</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>280.8</v>
+        <v>425.36</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>556.8099999999999</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>144.56</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>6179.94</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>425.36</v>
+        <v>982.17</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>425.36</v>
+        <v>982.17</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>91.58</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -2423,52 +2423,52 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>1 de 31</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>1 de 31</t>
-        </is>
-      </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>2 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3199,7 +3199,7 @@
         <v>5430.51</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>173.23</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>982.17</v>
+        <v>1155.4</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>568.8</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>91.58</v>
+        <v>2747.52</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0</v>
+        <v>199.44</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0</v>
@@ -2443,47 +2443,47 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
+          <t>1 de 31</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>2 de 31</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>0 de 31</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>1 de 31</t>
         </is>
       </c>
-      <c r="J33" s="3" t="inlineStr">
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>2 de 31</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr">
         <is>
           <t>0 de 31</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>1 de 31</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>2 de 31</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
+        <v>594.9</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>5430.51</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>173.23</v>
+        <v>3028.61</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1155.4</v>
+        <v>4605.68</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="27" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3528,13 +3528,13 @@
         <v>240</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
+        <v>568.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>240</v>
+        <v>-328.8</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="5">
@@ -3552,10 +3552,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>280.8</v>
+        <v>506.34</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-280.8</v>
+        <v>-506.34</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
@@ -3619,13 +3619,13 @@
         <v>15284.5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>275.4</v>
+        <v>1069.74</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15009.1</v>
+        <v>14214.76</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.01801825378651575</v>
+        <v>0.06998855049232881</v>
       </c>
     </row>
   </sheetData>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>4180.67</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>556.8099999999999</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>144.56</v>
+        <v>5367.45</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>3 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
         <v>265.58</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>4180.67</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>6179.94</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>982.17</v>
+        <v>6205.06</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4605.68</v>
+        <v>14009.24</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4180.67</v>
+        <v>4252.95</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>265.58</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4180.67</v>
+        <v>4252.95</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>14009.24</v>
+        <v>14081.52</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4252.95</v>
+        <v>5608.65</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>81.65000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -3064,7 +3064,7 @@
         <v>265.58</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>4252.95</v>
+        <v>5608.65</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>5430.51</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3028.61</v>
+        <v>3034.32</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>13604.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>14081.52</v>
+        <v>15442.93</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>568.8</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5608.65</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>280.8</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>556.8099999999999</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5367.45</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2747.52</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>87.36</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>199.44</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2443,12 +2443,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>3 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -2513,10 +2513,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>diciembre</t>
+          <t>enero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2596,16 +2596,16 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>388.8</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>388.8</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>594.9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>594.9</v>
+        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -2974,13 +2974,13 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>2198.58</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2198.58</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>610.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>0</v>
@@ -3001,13 +3001,13 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>1971.92</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1971.92</v>
+        <v>1118.05</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1118.05</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>0</v>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>3124.48</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3124.48</v>
+        <v>265.58</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>265.58</v>
+        <v>5608.65</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5608.65</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>5875.71</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>5875.71</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>2719.84</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>96.37</v>
+        <v>1442.48</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1442.48</v>
+        <v>6179.94</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6179.94</v>
+        <v>6205.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6205.06</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3193,13 +3193,13 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>5430.51</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5430.51</v>
+        <v>3034.32</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3034.32</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3396,16 +3396,16 @@
     </row>
     <row r="33">
       <c r="C33" s="4" t="n">
-        <v>96.37</v>
+        <v>17721.81</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>17721.81</v>
+        <v>13604.64</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>13604.64</v>
+        <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>15442.93</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>-51.54</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3145,7 +3145,7 @@
         <v>6205.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>-51.54</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>-51.54</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>0</v>
+        <v>51.97</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
         <v>5608.65</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>51.97</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-51.54</v>
+        <v>0.4299999999999997</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>574.01</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-51.54</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>6205.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-51.54</v>
+        <v>574.01</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.4299999999999997</v>
+        <v>625.98</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>51.97</v>
+        <v>120.83</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0</v>
+        <v>174.6</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -3064,7 +3064,7 @@
         <v>5608.65</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>51.97</v>
+        <v>120.83</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>3034.32</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>174.6</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>625.98</v>
+        <v>869.4399999999999</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>574.01</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>352.51</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>2 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
         <v>6205.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>574.01</v>
+        <v>926.52</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>869.4399999999999</v>
+        <v>1221.95</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>914.28</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>2 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3199,7 +3199,7 @@
         <v>3034.32</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>174.6</v>
+        <v>1088.88</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1221.95</v>
+        <v>2136.23</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0</v>
+        <v>472.09</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -3199,7 +3199,7 @@
         <v>3034.32</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1088.88</v>
+        <v>1560.97</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2136.23</v>
+        <v>2608.32</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>574.01</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>352.51</v>
+        <v>1621.56</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
         <v>6205.06</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>926.52</v>
+        <v>2195.57</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2608.32</v>
+        <v>3877.37</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>472.09</v>
+        <v>1022.86</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>914.28</v>
+        <v>1371.51</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>3034.32</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1560.97</v>
+        <v>2568.97</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>15442.93</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3877.37</v>
+        <v>4885.37</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1677,7 +1677,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>574.01</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1621.56</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1022.86</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -1974,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1371.51</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>174.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="2" t="n">
         <v>0</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>1 de 31</t>
+          <t>0 de 31</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>enero</t>
+          <t>febrero</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>388.8</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0</v>
+        <v>594.9</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>594.9</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>2198.58</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>610.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1971.92</v>
+        <v>1118.05</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1118.05</v>
+        <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -3055,16 +3055,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>3124.48</v>
+        <v>265.58</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>265.58</v>
+        <v>5608.65</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5608.65</v>
+        <v>120.83</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5875.71</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2719.84</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1442.48</v>
+        <v>6179.94</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6179.94</v>
+        <v>6205.06</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>6205.06</v>
+        <v>2195.57</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>2195.57</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0</v>
+        <v>5430.51</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>5430.51</v>
+        <v>3034.32</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>3034.32</v>
+        <v>2568.97</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2568.97</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3396,16 +3396,16 @@
     </row>
     <row r="33">
       <c r="C33" s="4" t="n">
-        <v>17721.81</v>
+        <v>13604.64</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>13604.64</v>
+        <v>15442.93</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>15442.93</v>
+        <v>4885.37</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4885.37</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>170.48</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>0 de 31</t>
+          <t>1 de 31</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3145,7 +3145,7 @@
         <v>2195.57</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>170.48</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3405,7 +3405,7 @@
         <v>4885.37</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0</v>
+        <v>170.48</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2508,11 +2508,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
+          <t>ARELLANO MACIAS NELSON BOLIVAR</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAESCORP S.A.S.</t>
+          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
+          <t>BAESCORP S.A.S.</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DELGADO COPPIANO JORGE RODOLFO</t>
+          <t>CEDEÑO ALAVA SANDRA ELIZABETH</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DELGADO LOOR JORGE ARTURO</t>
+          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DISALME CIA. LTDA.</t>
+          <t>DECORAHOGAR S.A.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRANQUICIA DISTRIBUIDORA SANTA MARIA FRADISAMA S.A.</t>
+          <t>FARIAS ANDRADE JOSE MANUEL</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2970,11 +2970,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>GALARRAGA CEVALLOS SARA VIRGINIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>610.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0</v>
@@ -2997,11 +2997,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1118.05</v>
+        <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0</v>
@@ -3024,11 +3024,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>610.5599999999999</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -3051,17 +3051,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>265.58</v>
+        <v>1118.05</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>5608.65</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>265.58</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>5608.65</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>120.83</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -3132,20 +3132,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6179.94</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6205.06</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2195.57</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>170.48</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3186,20 +3186,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5430.51</v>
+        <v>6179.94</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>3034.32</v>
+        <v>6205.06</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2568.97</v>
+        <v>2195.57</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>170.48</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0</v>
+        <v>5430.51</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0</v>
+        <v>3034.32</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>2568.97</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3294,14 +3294,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>SANCHEZ SABANDO LUIS JAVIER</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0</v>
+        <v>-5.4</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -3375,39 +3375,147 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>VERA ARCE MARIA ISABEL</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="4" t="n">
-        <v>13604.64</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>15442.93</v>
-      </c>
-      <c r="E33" s="4" t="n">
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ZAMBRANO TAPIA LUIS ANGEL</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="4" t="n">
+        <v>13610.04</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>15437.53</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>4885.37</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F37" s="4" t="n">
         <v>170.48</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -440,11 +440,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
+          <t>CEDEÑO ALAVA SANDRA ELIZABETH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DELGADO COPPIANO JORGE RODOLFO</t>
+          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DELGADO LOOR JORGE ARTURO</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DISALME CIA. LTDA.</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRANQUICIA DISTRIBUIDORA SANTA MARIA FRADISAMA S.A.</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>170.48</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>170.48</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>SANCHEZ SABANDO LUIS JAVIER</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SOLORZANO BRAVO TERESA CONCEPCION</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2296,204 +2296,84 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>1 de 31</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>0 de 31</t>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>0 de 29</t>
         </is>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1737,7 +1737,7 @@
         <v>170.48</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>1123.08</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3079,7 +3079,7 @@
         <v>2195.57</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>170.48</v>
+        <v>1293.56</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>170.48</v>
+        <v>1293.56</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>1497.6</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1603.3</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>2377.58</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -2298,52 +2298,52 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>5478.48</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1293.56</v>
+        <v>6772.039999999999</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1593,7 +1593,7 @@
         <v>1603.3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>1072.13</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2377.58</v>
+        <v>6782.22</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>5478.48</v>
+        <v>11559.94</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6772.039999999999</v>
+        <v>12853.5</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>2203.08</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3079,7 +3079,7 @@
         <v>2195.57</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>1293.56</v>
+        <v>3496.64</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>12853.5</v>
+        <v>15056.58</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>4380.36</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2203.08</v>
+        <v>2281.76</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3052,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>4380.36</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>2195.57</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3496.64</v>
+        <v>3575.32</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>15056.58</v>
+        <v>19515.62</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1497.6</v>
+        <v>1382.4</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>1603.3</v>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11559.94</v>
+        <v>11444.74</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>19515.62</v>
+        <v>19400.42</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1737,7 +1737,7 @@
         <v>170.48</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1123.08</v>
+        <v>8007.73</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>2195.57</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3575.32</v>
+        <v>10459.97</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>19400.42</v>
+        <v>26285.07</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1737,7 +1737,7 @@
         <v>170.48</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>8007.73</v>
+        <v>14579.44</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>2195.57</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>10459.97</v>
+        <v>17031.68</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>26285.07</v>
+        <v>32856.78</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>4885.37</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>32856.78</v>
+        <v>33105.81</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>249.03</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1382.4</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1603.3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1072.13</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6782.22</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>4380.36</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2281.76</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>170.48</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>14579.44</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2298,17 +2298,17 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2395,8 +2395,8 @@
     <col width="49" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2413,22 +2413,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>febrero</t>
+          <t>marzo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>594.9</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>594.9</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>610.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -2935,16 +2935,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1118.05</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>249.03</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>265.58</v>
+        <v>5608.65</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>5608.65</v>
+        <v>120.83</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -3022,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0</v>
+        <v>11444.74</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>11444.74</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3049,10 +3049,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>4380.36</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>4380.36</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -3070,16 +3070,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6179.94</v>
+        <v>6205.06</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>6205.06</v>
+        <v>2195.57</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2195.57</v>
+        <v>17031.68</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>17031.68</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3124,13 +3124,13 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5430.51</v>
+        <v>3034.32</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>3034.32</v>
+        <v>2568.97</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2568.97</v>
+        <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0</v>
@@ -3178,10 +3178,10 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5.4</v>
+        <v>-5.4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -3384,16 +3384,16 @@
     </row>
     <row r="37">
       <c r="C37" s="4" t="n">
-        <v>13610.04</v>
+        <v>15437.53</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>15437.53</v>
+        <v>4885.37</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>4885.37</v>
+        <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>33105.81</v>
+        <v>0</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0</v>
+        <v>2971.8</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0</v>
+        <v>89.17</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1854,13 +1854,13 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1103</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0</v>
+        <v>1598.51</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -2303,57 +2303,57 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2944,7 +2944,7 @@
         <v>249.03</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>2971.8</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0</v>
+        <v>2790.68</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>5762.48</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>-18.86</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>249.03</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2971.8</v>
+        <v>2952.94</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5762.48</v>
+        <v>5743.62</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>31.84</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -3079,7 +3079,7 @@
         <v>17031.68</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>0</v>
+        <v>31.84</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5743.62</v>
+        <v>5775.46</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>4463.15</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>3056.87</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>1085.27</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -3025,7 +3025,7 @@
         <v>11444.74</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>0</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5775.46</v>
+        <v>14380.75</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -3079,7 +3079,7 @@
         <v>17031.68</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>31.84</v>
+        <v>37.24</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>14380.75</v>
+        <v>14386.15</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>89.17</v>
+        <v>235.29</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>2790.68</v>
+        <v>2936.8</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>14386.15</v>
+        <v>14532.27</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>31.84</v>
+        <v>38.16</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         <v>17031.68</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>37.24</v>
+        <v>43.56</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>14532.27</v>
+        <v>14565.98</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>6537.47</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3052,7 +3052,7 @@
         <v>4380.36</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>0</v>
+        <v>6537.47</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>33105.81</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>14565.98</v>
+        <v>21103.45</v>
       </c>
       <c r="G37" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2388,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FARIAS ANDRADE JOSE MANUEL</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>GALARRAGA CEVALLOS SARA VIRGINIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GALARRAGA CEVALLOS SARA VIRGINIA</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>2952.94</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
@@ -2941,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>249.03</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2952.94</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>5608.65</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>120.83</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -2985,20 +2985,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5608.65</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>11444.74</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>27.39</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3022,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>11444.74</v>
+        <v>4380.36</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>8605.290000000001</v>
+        <v>6537.47</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3039,20 +3039,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0</v>
+        <v>6205.06</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0</v>
+        <v>2195.57</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4380.36</v>
+        <v>17031.68</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>6537.47</v>
+        <v>43.56</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -3066,20 +3066,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6205.06</v>
+        <v>0</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2195.57</v>
+        <v>0</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>17031.68</v>
+        <v>0</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>43.56</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>0</v>
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0</v>
+        <v>3034.32</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0</v>
+        <v>2568.97</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>0</v>
+        <v>2936.8</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -3120,20 +3120,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>3034.32</v>
+        <v>0</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2568.97</v>
+        <v>0</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>2936.8</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>0</v>
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
+          <t>SANCHEZ SABANDO LUIS JAVIER</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0</v>
+        <v>-5.4</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -3174,11 +3174,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SANCHEZ SABANDO LUIS JAVIER</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
+          <t>ZAMBRANO TAPIA LUIS ANGEL</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -3356,46 +3356,19 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ZAMBRANO TAPIA LUIS ANGEL</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" s="4" t="n">
+      <c r="C36" s="4" t="n">
         <v>15437.53</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D36" s="4" t="n">
         <v>4885.37</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E36" s="4" t="n">
         <v>33105.81</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F36" s="4" t="n">
         <v>21103.45</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2388,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARELLANO MACIAS NELSON BOLIVAR</t>
+          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
+          <t>BAESCORP S.A.S.</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAESCORP S.A.S.</t>
+          <t>CEDEÑO ALAVA SANDRA ELIZABETH</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CEDEÑO ALAVA SANDRA ELIZABETH</t>
+          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DECORAHOGAR S.A.</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DELGADO COPPIANO JORGE RODOLFO</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FREILE FERRIN FRECIA NOEMI LOURDE</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2806,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>2952.94</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GALARRAGA CEVALLOS SARA VIRGINIA</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
@@ -2850,20 +2850,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>5608.65</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>120.83</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -2887,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>11444.74</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
@@ -2914,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>249.03</v>
+        <v>4380.36</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2952.94</v>
+        <v>6537.47</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2931,20 +2931,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>6205.06</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>2195.57</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0</v>
+        <v>17031.68</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>43.56</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2958,20 +2958,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5608.65</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>27.39</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>0</v>
@@ -2985,20 +2985,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>3034.32</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2568.97</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>11444.74</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>8605.290000000001</v>
+        <v>2936.8</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3022,10 +3022,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4380.36</v>
+        <v>0</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6537.47</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0</v>
@@ -3039,20 +3039,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>SANCHEZ SABANDO LUIS JAVIER</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6205.06</v>
+        <v>-5.4</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>2195.57</v>
+        <v>0</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>17031.68</v>
+        <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>43.56</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3093,20 +3093,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>3034.32</v>
+        <v>0</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>2568.97</v>
+        <v>0</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>2936.8</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>0</v>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3147,11 +3147,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SANCHEZ SABANDO LUIS JAVIER</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -3221,154 +3221,19 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>VERA ARCE MARIA ISABEL</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ZAMBRANO TAPIA LUIS ANGEL</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" s="4" t="n">
+      <c r="C31" s="4" t="n">
         <v>15437.53</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D31" s="4" t="n">
         <v>4885.37</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E31" s="4" t="n">
         <v>33105.81</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>21103.45</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1431,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-18.86</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2971.8</v>
+        <v>0</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27.39</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4463.15</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>3056.87</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1085.27</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6537.47</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>38.16</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>235.29</v>
+        <v>0</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
@@ -1854,13 +1854,13 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1103</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1598.51</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -2394,9 +2394,9 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2413,22 +2413,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>marzo</t>
+          <t>abril</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>594.9</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>249.03</v>
+        <v>2952.94</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2952.94</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5608.65</v>
+        <v>120.83</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>27.39</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
+        <v>11444.74</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11444.74</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>8605.290000000001</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2911,13 +2911,13 @@
         <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>4380.36</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4380.36</v>
+        <v>6537.47</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>6537.47</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2935,16 +2935,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>6205.06</v>
+        <v>2195.57</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2195.57</v>
+        <v>17031.68</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>17031.68</v>
+        <v>43.56</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>43.56</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2989,16 +2989,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>3034.32</v>
+        <v>2568.97</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2568.97</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>2936.8</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2936.8</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3043,7 +3043,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-5.4</v>
+        <v>0</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="31">
       <c r="C31" s="4" t="n">
-        <v>15437.53</v>
+        <v>4885.37</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4885.37</v>
+        <v>33105.81</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>33105.81</v>
+        <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>21103.45</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>601.23</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2863,7 +2863,7 @@
         <v>27.39</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>601.23</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>601.23</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>571.54</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>23.37</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2944,7 +2944,7 @@
         <v>43.56</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>594.91</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>601.23</v>
+        <v>1196.14</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
+        <v>72.63</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
         <v>2936.8</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>72.63</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1196.14</v>
+        <v>1268.77</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>601.23</v>
+        <v>653.83</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>27.39</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>601.23</v>
+        <v>653.83</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1268.77</v>
+        <v>1321.37</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>1159.83</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>6479.42</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1238.42</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>146.97</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>72.63</v>
@@ -2298,52 +2298,52 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2917,7 +2917,7 @@
         <v>6537.47</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>8877.67</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2998,7 +2998,7 @@
         <v>2936.8</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>72.63</v>
+        <v>219.6</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1321.37</v>
+        <v>10346.01</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0</v>
+        <v>312.26</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>146.97</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>72.63</v>
+        <v>3077.79</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2298,7 +2298,7 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2998,7 +2998,7 @@
         <v>2936.8</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>219.6</v>
+        <v>3537.02</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10346.01</v>
+        <v>13663.43</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>1040.86</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1499.05</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>4592.84</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -2298,14 +2298,14 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>3 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
           <t>2 de 29</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>1 de 29</t>
-        </is>
-      </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>4 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2890,7 +2890,7 @@
         <v>8605.290000000001</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>7132.75</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21103.45</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>13663.43</v>
+        <v>20796.18</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>653.83</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1040.86</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1499.05</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4592.84</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1159.83</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>6479.42</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1238.42</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>571.54</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>23.37</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>312.26</v>
+        <v>0</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>146.97</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3077.79</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="n">
         <v>0</v>
@@ -2298,12 +2298,12 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2393,10 +2393,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2413,22 +2413,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>abril</t>
+          <t>mayo</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2800,13 +2800,13 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0</v>
+        <v>249.03</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>249.03</v>
+        <v>2952.94</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2952.94</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>0</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>120.83</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>27.39</v>
+        <v>653.83</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>653.83</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2881,16 +2881,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0</v>
+        <v>11444.74</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>11444.74</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8605.290000000001</v>
+        <v>7979.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>7132.75</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>4380.36</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>4380.36</v>
+        <v>6537.47</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>6537.47</v>
+        <v>8877.67</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>8877.67</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2935,16 +2935,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2195.57</v>
+        <v>17031.68</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>17031.68</v>
+        <v>43.56</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43.56</v>
+        <v>594.91</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>594.91</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2989,16 +2989,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2568.97</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0</v>
+        <v>2936.8</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2936.8</v>
+        <v>3537.02</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3537.02</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="31">
       <c r="C31" s="4" t="n">
-        <v>4885.37</v>
+        <v>33105.81</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>33105.81</v>
+        <v>21103.45</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21103.45</v>
+        <v>21642.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>20796.18</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>861.02</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2944,7 +2944,7 @@
         <v>594.91</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0</v>
+        <v>861.02</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21642.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>861.02</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>3216.77</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2998,7 +2998,7 @@
         <v>3537.02</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>0</v>
+        <v>3216.77</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21642.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>861.02</v>
+        <v>4077.79</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0</v>
+        <v>966.51</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
+        <v>9327.129999999999</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>5212.34</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -2298,52 +2298,52 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>1 de 29</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>0 de 29</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>0 de 29</t>
-        </is>
-      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>3 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2917,7 +2917,7 @@
         <v>8877.67</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>15505.98</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21642.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4077.79</v>
+        <v>19583.77</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>6420.1</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5212.34</v>
+        <v>7243.98</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>861.02</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>27.38</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>3216.77</v>
+        <v>5615.24</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2863,7 +2863,7 @@
         <v>653.83</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>6420.1</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>8877.67</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>15505.98</v>
+        <v>17537.62</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>594.91</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>861.02</v>
+        <v>888.4</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2998,7 +2998,7 @@
         <v>3537.02</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>3216.77</v>
+        <v>5615.24</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21642.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>19583.77</v>
+        <v>30461.36</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>416.34</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>1983.44</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>6141.25</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>0</v>
+        <v>1468.94</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -2298,12 +2298,12 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
+          <t>4 de 29</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
           <t>3 de 29</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>2 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2890,7 +2890,7 @@
         <v>7979.27</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>10009.97</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>21642.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>30461.36</v>
+        <v>40471.33</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>6420.1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>416.34</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1983.44</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -1614,10 +1614,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6141.25</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1468.94</v>
+        <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
         <v>0</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>966.51</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9327.129999999999</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7243.98</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>861.02</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>27.38</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5615.24</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -2298,12 +2298,12 @@
     <row r="31">
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>2 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>3 de 29</t>
+          <t>0 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2393,10 +2393,10 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2413,22 +2413,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mayo</t>
+          <t>junio</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>junio</t>
+          <t>julio</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>julio</t>
+          <t>agosto</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>agosto</t>
+          <t>septiembre</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>249.03</v>
+        <v>2952.94</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2952.94</v>
+        <v>0</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>27.39</v>
+        <v>653.83</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>653.83</v>
+        <v>6420.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6420.1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2881,16 +2881,16 @@
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>11444.74</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8605.290000000001</v>
+        <v>7979.27</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7979.27</v>
+        <v>10009.97</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>10009.97</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2908,16 +2908,16 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>4380.36</v>
+        <v>6537.47</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>6537.47</v>
+        <v>8877.67</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>8877.67</v>
+        <v>17537.62</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>17537.62</v>
+        <v>0</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2935,16 +2935,16 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>17031.68</v>
+        <v>43.56</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>43.56</v>
+        <v>594.91</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>594.91</v>
+        <v>888.4</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>888.4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0</v>
@@ -2989,16 +2989,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>0</v>
+        <v>2936.8</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2936.8</v>
+        <v>3537.02</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>3537.02</v>
+        <v>5615.24</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>5615.24</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="31">
       <c r="C31" s="4" t="n">
-        <v>33105.81</v>
+        <v>21103.45</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>21103.45</v>
+        <v>21642.7</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>21642.7</v>
+        <v>40471.33</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>40471.33</v>
+        <v>0</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>-104.09</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
         <v>10009.97</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>-104.09</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>40471.33</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
+        <v>-104.09</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1554,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>253.96</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>0</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2863,7 +2863,7 @@
         <v>6420.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>253.96</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -3231,7 +3231,7 @@
         <v>40471.33</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-104.09</v>
+        <v>149.87</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2388,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARELLANO CEDEÑO DANNY MARCELO</t>
+          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ARMIJOS BARCIA FRACISCO ANTONIO</t>
+          <t>BAESCORP S.A.S.</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAESCORP S.A.S.</t>
+          <t>CEDEÑO ALAVA SANDRA ELIZABETH</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CEDEÑO ALAVA SANDRA ELIZABETH</t>
+          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHANGKUON AYON JOSE CRISTOBAL</t>
+          <t>DELGADO COPPIANO JORGE RODOLFO</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DELGADO COPPIANO JORGE RODOLFO</t>
+          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FERRETERIA UNIDA ZAMBRANO FERRUZAM CIA. LTDA.</t>
+          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GONZALEZ CARDENAS ERNESTO PAOLO</t>
+          <t>GRANIMUNDO S.A.</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
@@ -2769,11 +2769,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GRANIMUNDO S.A.</t>
+          <t>LINO TUMBACO VICENTE JAVIER</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0</v>
+        <v>2952.94</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0</v>
@@ -2796,11 +2796,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINO TUMBACO VICENTE JAVIER</t>
+          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2952.94</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0</v>
@@ -2823,20 +2823,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MANABITA DE REPUESTOS MANARECO C LTDA</t>
+          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0</v>
+        <v>27.39</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
+        <v>653.83</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>6420.1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0</v>
+        <v>253.96</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -2850,20 +2850,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MATERIALES PARA DECORACION DECORCASA CIA. LTDA.</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>27.39</v>
+        <v>6537.47</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>653.83</v>
+        <v>8877.67</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>6420.1</v>
+        <v>17537.62</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>253.96</v>
+        <v>0</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2877,20 +2877,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>8605.290000000001</v>
+        <v>43.56</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>7979.27</v>
+        <v>594.91</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>10009.97</v>
+        <v>888.4</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-104.09</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2904,17 +2904,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>6537.47</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8877.67</v>
+        <v>0</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>17537.62</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>0</v>
@@ -2931,17 +2931,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>43.56</v>
+        <v>2936.8</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>594.91</v>
+        <v>3537.02</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>888.4</v>
+        <v>5615.24</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>SANCHEZ SABANDO LUIS JAVIER</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>2936.8</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>3537.02</v>
+        <v>0</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>5615.24</v>
+        <v>0</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANCHEZ SABANDO LUIS JAVIER</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -3167,73 +3167,19 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MEZA PEÑA CARLOS ROBERTO</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="4" t="n">
-        <v>21103.45</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>21642.7</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>40471.33</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>149.87</v>
-      </c>
-      <c r="G31" s="4" t="n">
+      <c r="C29" s="4" t="n">
+        <v>12498.16</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>13663.43</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>30461.36</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>253.96</v>
+      </c>
+      <c r="G29" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1734,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>457.23</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1 de 29</t>
+          <t>2 de 29</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2890,7 +2890,7 @@
         <v>888.4</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>457.23</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>30461.36</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>253.96</v>
+        <v>711.1900000000001</v>
       </c>
       <c r="G29" s="4" t="n">
         <v>0</v>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -2388,7 +2388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2850,20 +2850,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PAREDES ORTIZ MARIA INES</t>
+          <t>MOREIRA MOREIRA PATRICIO IGNACIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6537.47</v>
+        <v>8605.290000000001</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8877.67</v>
+        <v>7979.27</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>17537.62</v>
+        <v>10009.97</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>-104.09</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -2877,20 +2877,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RENOVA&amp;DISEÑA S.A.</t>
+          <t>PAREDES ORTIZ MARIA INES</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>43.56</v>
+        <v>6537.47</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>594.91</v>
+        <v>8877.67</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>888.4</v>
+        <v>17537.62</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>457.23</v>
+        <v>0</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0</v>
@@ -2904,20 +2904,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>REYES AGUILERA JESSICA ELIZABETH</t>
+          <t>RENOVA&amp;DISEÑA S.A.</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>0</v>
+        <v>43.56</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0</v>
+        <v>594.91</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0</v>
+        <v>888.4</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0</v>
+        <v>457.23</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>0</v>
@@ -2931,17 +2931,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ROCA REYNA PAUL DAVID</t>
+          <t>REYES AGUILERA JESSICA ELIZABETH</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2936.8</v>
+        <v>0</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>3537.02</v>
+        <v>0</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>5615.24</v>
+        <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>0</v>
@@ -2958,17 +2958,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
+          <t>ROCA REYNA PAUL DAVID</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0</v>
+        <v>2936.8</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0</v>
+        <v>3537.02</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0</v>
+        <v>5615.24</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANCHEZ SABANDO LUIS JAVIER</t>
+          <t>RODRIGUEZ ACUÑA LUIS ANTONIO</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SUMBA GARCIA MARCOS ANTONIO</t>
+          <t>SANCHEZ SABANDO LUIS JAVIER</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
+          <t>SUMBA GARCIA MARCOS ANTONIO</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
+          <t>TUTIVEN PAREDES MARCIA PIEDAD</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VERA ARCE MARIA ISABEL</t>
+          <t>VACA CANCHINGRE FATIMA YAQUELINE</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+          <t>VERA ARCE MARIA ISABEL</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
@@ -3147,39 +3147,66 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>ZAMBRANO FERNANDEZ JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MEZA PEÑA CARLOS ROBERTO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>ZAMBRANO REYNA JOSE ALEJANDRO</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" s="4" t="n">
-        <v>12498.16</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>13663.43</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>30461.36</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>711.1900000000001</v>
-      </c>
-      <c r="G29" s="4" t="n">
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="4" t="n">
+        <v>21103.45</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>21642.7</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>40471.33</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>607.1</v>
+      </c>
+      <c r="G30" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/MEZA PEÑA CARLOS ROBERTO.xlsx
+++ b/data/MEZA PEÑA CARLOS ROBERTO.xlsx
@@ -1557,7 +1557,7 @@
         <v>253.96</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>0</v>
+        <v>313.63</v>
       </c>
       <c r="N18" s="2" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>0 de 29</t>
+          <t>1 de 29</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -2836,7 +2836,7 @@
         <v>6420.1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>253.96</v>
+        <v>567.59</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
         <v>40471.33</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>607.1</v>
+        <v>920.73</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>0</v>
